--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M6B10_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M6B10_IN_Piura.xlsx
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>0.17</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>18.59</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C13" s="31">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>50.9</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>30.34</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="B15" s="45">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>249.8905</v>
       </c>
       <c r="C15" s="46">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="44" t="inlineStr">
         <is>
@@ -1948,11 +1948,11 @@
       </c>
       <c r="B16" s="48">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>0.4365</v>
       </c>
       <c r="C16" s="49">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>0.17</v>
       </c>
       <c r="D16" s="47" t="inlineStr">
         <is>
@@ -1973,11 +1973,11 @@
       </c>
       <c r="B17" s="48">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>249.454</v>
       </c>
       <c r="C17" s="49">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>99.83</v>
       </c>
       <c r="D17" s="47" t="inlineStr">
         <is>
@@ -2171,11 +2171,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>250.0039</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2294,6 +2294,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2471,6 +2472,7 @@
       <c r="F14" s="17" t="inlineStr"/>
       <c r="G14" s="17" t="inlineStr"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
@@ -2515,6 +2517,7 @@
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="8" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19" ht="132" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
@@ -2833,11 +2836,11 @@
       </c>
       <c r="B15" s="33">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>1553.97</v>
       </c>
       <c r="C15" s="23">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -2847,19 +2850,19 @@
       <c r="E15" s="17" t="inlineStr"/>
       <c r="F15" s="17">
         <f>ROUND(AVERAGE(F10:F14),2)</f>
-        <v/>
+        <v>18.02</v>
       </c>
       <c r="G15" s="22">
         <f>ROUND(AVERAGE(G10:G14),4)</f>
-        <v/>
+        <v>0.3393</v>
       </c>
       <c r="H15" s="23">
         <f>ROUND(AVERAGE(H10:H14),2)</f>
-        <v/>
+        <v>2.45</v>
       </c>
       <c r="I15" s="23">
         <f>ROUND(AVERAGE(I10:I14),2)</f>
-        <v/>
+        <v>97.63</v>
       </c>
     </row>
     <row r="16"/>
